--- a/src-tauri/resources/input_template.xlsx
+++ b/src-tauri/resources/input_template.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教师名单" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="班级名单" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="课程信息" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教师" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="班级" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="课时标准" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,12 +30,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -47,12 +41,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002563EB"/>
-        <bgColor rgb="002563EB"/>
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -60,25 +54,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -153,6 +137,21 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>排课助手</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>只需填写参与排课决策的教师（语数英、物化生政史地等）。体育、艺术、体育活动等科目不需要填写教师，课表也不显示教师姓名。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -444,140 +443,259 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>教师ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>教师姓名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>任教学科</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>所教班级</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>周课时数</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>职务</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>T001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>张老师</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>语文</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>1班,2班</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>班主任</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>李老师</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>语文</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>王老师</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>数学</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>3班,4班</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>王老师</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>班主任</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>赵老师</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>刘老师</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>英语</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1班,5班</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>周二下午有会</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>赵老师</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>班主任</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>T006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>陈老师</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>周老师</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>物理</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>5班,6班,7班</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>说明：所教班级用逗号分隔；周课时数是该老师每周总共要上的节数</t>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>T008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>吴老师</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>化学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>T009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>郑老师</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>生物</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>孙老师</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>政治</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>钱老师</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>历史</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>冯老师</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>地理</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -587,142 +705,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>班级编号</t>
+          <t>班级ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>班级类型</t>
+          <t>班级名称</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>年级</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>班主任</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>学生人数</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>选科</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>文科班</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>张老师</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>高二(1)班</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>T001</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>物化生</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>文科班</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>李老师</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>高二(2)班</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>T003</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>物化地</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>文科班</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>王老师</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>理科班</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>赵老师</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>理科班</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>钱老师</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>说明：班级类型填「文科班」或「理科班」；班主任姓名需与教师名单一致</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>高二(3)班</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>T005</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>政史地</t>
         </is>
       </c>
     </row>
@@ -737,14 +834,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -755,144 +852,308 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>每周节数</t>
+          <t>选考周课时</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>是否连堂</t>
+          <t>非选考周课时</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>连堂要求</t>
+          <t>连堂节数</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>连堂日</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>语文</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>物理</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>周三上午连堂</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>数学</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>历史</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>周二上午连堂</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>英语</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>周四上午连堂</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>物理</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>化学</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>历史</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>生物</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>政治</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>地理</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>体育</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B11" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>说明：每周节数是每个班每周该学科的总节数；连堂要求与硬限制设置对应</t>
-        </is>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>体育活动</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>艺术</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>班会</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>研究性学习</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>校本课</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/src-tauri/resources/input_template.xlsx
+++ b/src-tauri/resources/input_template.xlsx
@@ -10,6 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教师" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="班级" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="课时标准" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="走班时间" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="走班教学班" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,8 +33,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +48,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDDDDD"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,10 +68,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1159,4 +1172,179 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>独立时间ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>周次数</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>连排节数</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>参与班级</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>走班1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>C02,C03</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>教学班ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>独立时间</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>学科</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>来源班级</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>人数</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>教室</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>任课教师</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>地理走班1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>走班1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>地理</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>走班教室1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>政治走班1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>走班1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>政治</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>C03教室</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>